--- a/output/pdf_financials_xlsx/CRRX.xlsx
+++ b/output/pdf_financials_xlsx/CRRX.xlsx
@@ -3210,37 +3210,37 @@
         <v>1.888</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>37.947</v>
+        <v>1.645</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>234.806</v>
+        <v>0.91</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.551</v>
+        <v>1.551</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1.044</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.255</v>
+        <v>0.897</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>27.266</v>
+        <v>1.2</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.982</v>
+        <v>2.839</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.297</v>
+        <v>2.561</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.886</v>
+        <v>1.958</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.508</v>
+        <v>1.952</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.726</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="49">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/pdf_financials_xlsx/CRRX.xlsx
+++ b/output/pdf_financials_xlsx/CRRX.xlsx
@@ -3210,37 +3210,37 @@
         <v>1.888</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.645</v>
+        <v>37.947</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.91</v>
+        <v>234.806</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.551</v>
+        <v>4.551</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1.044</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.897</v>
+        <v>1.255</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.2</v>
+        <v>27.266</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.839</v>
+        <v>3.982</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.561</v>
+        <v>3.297</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.958</v>
+        <v>2.886</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.952</v>
+        <v>2.508</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.17</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="49">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -51494,7 +51494,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -74957,7 +74957,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E762" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRRX.xlsx
+++ b/output/pdf_financials_xlsx/CRRX.xlsx
@@ -2176,28 +2176,28 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>3.209</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>3.523</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>4.179</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>6.967</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>9.428000000000001</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>9.725</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>9.361000000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="29">
@@ -2240,28 +2240,28 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.89</v>
+        <v>-3.681</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-37.714</v>
+        <v>-34.191</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-33.529</v>
+        <v>-29.35</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-23.735</v>
+        <v>-16.768</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-35.896</v>
+        <v>-26.468</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-9.595000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.469</v>
+        <v>4.892</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.353</v>
+        <v>13.615</v>
       </c>
     </row>
     <row r="30">
@@ -2304,28 +2304,28 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-5.647124392462851</v>
+        <v>-3.016990549877468</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-30.47792988637649</v>
+        <v>-27.63087714761358</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-28.19482168534885</v>
+        <v>-24.68066499045569</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-9.037429082739976</v>
+        <v>-6.384647603091802</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-9.403578997555845</v>
+        <v>-6.933751083889796</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-2.588025224816991</v>
+        <v>0.03506443764733807</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-1.218660863779403</v>
+        <v>1.33400960966857</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.905626335278913</v>
+        <v>3.677334492938384</v>
       </c>
     </row>
     <row r="31">
@@ -5911,49 +5911,49 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>3.103</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>7.101</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>7.477</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.917</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5.369</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.821</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>3.209</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.523</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>4.179</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>6.967</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>9.428000000000001</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>9.725</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>9.361000000000001</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>10.262</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -25659,7 +25659,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29031,7 +29035,11 @@
           <t>Depreciation of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34133,7 +34141,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -40094,7 +40106,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E369" s="5" t="n">
         <v>0.266</v>
       </c>
@@ -40713,7 +40729,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -41785,7 +41805,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -43225,7 +43249,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -43759,7 +43787,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -45917,7 +45949,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E434" s="5" t="n">
         <v>0.007</v>
       </c>

--- a/output/pdf_financials_xlsx/CRRX.xlsx
+++ b/output/pdf_financials_xlsx/CRRX.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>4.354</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.334</v>
+        <v>7.688</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.262</v>
+        <v>4.19</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.928</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.169</v>
+        <v>2.509</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>6.621</v>
+        <v>3.326</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>4.222</v>
@@ -1646,13 +1646,13 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.279</v>
+        <v>-4.381</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-31.093</v>
+        <v>-34.388</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-29.307</v>
+        <v>-35.387</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-22.73</v>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>3.295</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.262</v>
+        <v>4.19</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.813</v>
+        <v>4.741</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>4.502096603821901</v>
+        <v>7.587785282161262</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>46.01431980906921</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-133.0769230769231</v>
+        <v>-36.41509433962264</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-17.55581481677891</v>
+        <v>-8.81900620459246</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-12.59208446419517</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>7.31</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>15.844</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>24.864</v>
+        <v>32.174</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>16.395</v>
@@ -3216,7 +3216,7 @@
         <v>234.806</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.551</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1.044</v>
@@ -3644,16 +3644,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>4.703</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>26.943</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>47.27</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -3696,16 +3696,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>3.254</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>6.357</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>13.458</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>20.935</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -3800,43 +3800,43 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>20.469</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>362.113</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>353.72</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>270.877</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>196.501</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>89.435</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>97.562</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>98.928</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>45.976</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>59.895</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>146.687</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>122.966</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>114.343</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0</v>
+        <v>19.029</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -3904,43 +3904,43 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>5.589</v>
+        <v>367.702</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>18.937</v>
+        <v>372.657</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>9.532</v>
+        <v>280.409</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>7.828</v>
+        <v>204.329</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>4.719</v>
+        <v>94.154</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>7.893</v>
+        <v>105.455</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>3.341</v>
+        <v>102.269</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>45.976</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>6.415</v>
+        <v>66.31</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0</v>
+        <v>146.687</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0</v>
+        <v>122.966</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0</v>
+        <v>114.343</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>104.315</v>
@@ -4066,43 +4066,43 @@
         <v>8.177</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>33.243</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>37.167</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>21.478</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>21.769</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>14.864</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>14.318</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>9.598000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>11.761</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>33.207</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>30.481</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>29.108</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>31.83</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>33.893</v>
       </c>
     </row>
     <row r="65">
@@ -4216,34 +4216,34 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>4.025</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>19.877</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>21.839</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>17.735</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>18.074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>11.168</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>7.225</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>5.463</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>4.921</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>6.086</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -4255,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>16.426</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>12.549</v>
       </c>
     </row>
     <row r="68">
@@ -4268,49 +4268,49 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>5.7</v>
+        <v>9.725</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8.177</v>
+        <v>28.054</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>55.082</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>54.902</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>39.552</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>32.937</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>22.089</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>19.781</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>14.519</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>17.847</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>33.207</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>30.481</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>29.108</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>48.256</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>46.442</v>
       </c>
     </row>
     <row r="69">
@@ -4632,49 +4632,49 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>279.372</v>
+        <v>259.495</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>92.062</v>
+        <v>36.98</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>66.79300000000001</v>
+        <v>11.891</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>59.23</v>
+        <v>19.678</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>93.895</v>
+        <v>60.958</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>61.681</v>
+        <v>39.592</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>106.105</v>
+        <v>86.324</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>68.021</v>
+        <v>53.502</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>112.583</v>
+        <v>94.736</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>52.44</v>
+        <v>19.233</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>61.289</v>
+        <v>30.808</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>59.65</v>
+        <v>30.542</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>60.013</v>
+        <v>11.757</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>60.261</v>
+        <v>13.819</v>
       </c>
     </row>
     <row r="76">
@@ -6290,34 +6290,34 @@
         <v>1.814</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>3.003</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>2.298</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>2.665</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>4.569</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>1.471</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>3.652</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>2.715</v>
       </c>
     </row>
     <row r="108">
@@ -6587,31 +6587,31 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-8.02</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-138.097</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-19.492</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-1.686</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>-25.244</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0</v>
+        <v>-11.942</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>-1.543</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
@@ -6743,49 +6743,49 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.292</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.292</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.512</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.258</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.853</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.452</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.259</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.857</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-1.489</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.412</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-1.765</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-3.571</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-3.967</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-2.526</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-2.713</v>
       </c>
     </row>
     <row r="117">
@@ -8684,7 +8684,11 @@
           <t>Goodwill and intangible assets, net (note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -11150,7 +11154,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -13183,7 +13187,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -15396,7 +15400,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -21212,7 +21216,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -22842,7 +22846,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
@@ -25993,7 +25997,11 @@
           <t>Share-based compensation expense (note 15)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -26645,7 +26653,11 @@
           <t>Purchase of intangible assets (note 7)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29389,7 +29401,11 @@
           <t>Share-based compensation expense (note 17)</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -30170,7 +30186,11 @@
           <t>Purchase of intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32545,7 +32565,11 @@
           <t>Acquisition of businesses</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -32899,7 +32923,11 @@
           <t>Net proceeds from March 2019 Private Placement</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -34398,7 +34426,11 @@
           <t>Share-based compensation expense (note 16)</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -34845,7 +34877,11 @@
           <t>Acquisition of businesses (note 3)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -35013,7 +35049,11 @@
           <t>Purchase of intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -36441,7 +36481,11 @@
           <t>Acquisition of businesses (note 2)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -42800,7 +42844,11 @@
           <t>Acquisition of businesses (note 6)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -44420,7 +44468,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E417" s="5" t="n">
         <v>-0.292</v>
       </c>
@@ -44598,7 +44650,11 @@
           <t>Acquisition of businesses (note 7)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -46044,7 +46100,11 @@
           <t>Acquisition of businesses (note 9)</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E435" s="5" t="n">
         <v>-8.02</v>
       </c>
@@ -48827,7 +48887,11 @@
           <t>Income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -50211,7 +50275,11 @@
           <t>Net loss from continuing operations (45,677)</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -50298,7 +50366,11 @@
           <t>Income from discontinued operations (note 21) 16,370</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -51787,7 +51859,11 @@
           <t>Income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -51872,7 +51948,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -51955,7 +52035,11 @@
           <t>Income from discontinued operations (note 19)</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -74635,7 +74719,11 @@
           <t>Corporate office expenses 11,284</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E758" s="5" t="n">
         <v>4.354</v>
       </c>
@@ -75533,7 +75621,11 @@
           <t>Income tax (recovery) expense (note 16) (1,918)</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E768" s="5" t="n">
         <v>1.928</v>
       </c>
